--- a/finential.xlsx
+++ b/finential.xlsx
@@ -615,33 +615,193 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>국가</t>
+          <t>순위</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>지수명</t>
+          <t>이름</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>현재가</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>등락률</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>시간</t>
+          <t>가격</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1.</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>339,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2.</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2,673,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3.</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>현대차</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>480,500</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4.</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>LG전자</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>195,900</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>5.</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>NAVER</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>196,400</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>6.</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>삼성전기</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1,993,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>7.</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>두산에너빌..</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>81,100</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>8.</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>한화오션</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>98,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>9.</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SK스퀘어</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1,720,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>10.</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>에코프로</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>95,400</t>
         </is>
       </c>
     </row>

--- a/finential.xlsx
+++ b/finential.xlsx
@@ -447,7 +447,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>339,500</t>
+          <t>323,000</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2,673,000</t>
+          <t>2,628,000</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>480,500</t>
+          <t>497,000</t>
         </is>
       </c>
     </row>
@@ -493,12 +493,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>195,900</t>
+          <t>118,000</t>
         </is>
       </c>
     </row>
@@ -510,12 +510,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NAVER</t>
+          <t>LG에너지솔..</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>196,400</t>
+          <t>400,500</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1,993,000</t>
+          <t>2,038,000</t>
         </is>
       </c>
     </row>
@@ -549,7 +549,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>81,100</t>
+          <t>88,000</t>
         </is>
       </c>
     </row>
@@ -561,12 +561,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>한화오션</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>98,000</t>
+          <t>196,700</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1,720,000</t>
+          <t>1,640,000</t>
         </is>
       </c>
     </row>
@@ -595,12 +595,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>95,400</t>
+          <t>512,000</t>
         </is>
       </c>
     </row>
@@ -615,193 +615,654 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>순위</t>
+          <t>국가</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>이름</t>
+          <t>지수명</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>가격</t>
+          <t>현재가</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>등락률</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>시간</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1.</t>
+          <t>미국</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>다우 산업</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>339,500</t>
+          <t>51,876.11</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-0.09%</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>06.26 16:20</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2.</t>
+          <t>미국</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>다우 운송</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2,673,000</t>
+          <t>21,825.83</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>-0.49%</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>06.26 16:20</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3.</t>
+          <t>미국</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>나스닥 종합</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>480,500</t>
+          <t>25,297.62</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>-0.24%</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>06.26 16:15</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>4.</t>
+          <t>미국</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>나스닥 100</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>195,900</t>
+          <t>29,118.24</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>-1.09%</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>06.26 16:15</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>5.</t>
+          <t>미국</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NAVER</t>
+          <t>S&amp;P 500</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>196,400</t>
+          <t>7,354.02</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>-0.05%</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>06.26 17:07</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6.</t>
+          <t>미국</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>필라델피아 반도체</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1,993,000</t>
+          <t>13,203.57</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>-5.29%</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>06.26 16:15</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>7.</t>
+          <t>브라질</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>두산에너빌..</t>
+          <t>브라질 BOVESPA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>81,100</t>
+          <t>173,295.14</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>+0.76%</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>06.26</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>8.</t>
+          <t>중국</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>한화오션</t>
+          <t>상해종합</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>98,000</t>
+          <t>4,073.90</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>+1.16%</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>06.29 15:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>9.</t>
+          <t>중국</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SK스퀘어</t>
+          <t>상해 A</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1,720,000</t>
+          <t>4,272.28</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>+1.16%</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>06.29 15:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10.</t>
+          <t>중국</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>상해 B</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>95,400</t>
+          <t>269.00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>+0.33%</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>06.29 15:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>니케이225</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>69,468.11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>+0.15%</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>06.29 15:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>홍콩</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>항셍</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>23,071.97</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>+1.76%</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>06.29 15:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>홍콩</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>항셍 차이나기업(H)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>7,624.87</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>+2.20%</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>06.29 15:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>홍콩</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>항셍 차이나대기업(R)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>3,769.08</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>+0.53%</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>06.29 15:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>대만</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>대만 가권</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>44,999.90</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>+0.96%</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>06.29 13:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>인도</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>인도 SENSEX</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>76,742.59</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>-0.46%</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>06.29 13:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>말레이시아</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>말레이시아 KLCI</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1,667.74</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>+0.24%</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>06.26 17:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>인도네시아</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>인도네시아 IDX종합</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>5,896.13</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>-1.72%</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>06.26</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>영국</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>영국 FTSE 100</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>10,495.03</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>-0.12%</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>06.29 08:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>프랑스</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>프랑스 CAC 40</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>8,373.58</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>-0.13%</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>06.29 09:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>독일</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>독일 DAX</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>24,726.01</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>+0.22%</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>06.29 09:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>유럽</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>유로스톡스 50</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>6,230.61</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>+0.15%</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>06.29 09:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>이탈리아</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>이탈리아 FTSE MIB</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>51,505.76</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>+0.46%</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>06.29 09:35</t>
         </is>
       </c>
     </row>
